--- a/app/tests/plans_export.xlsx
+++ b/app/tests/plans_export.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-11-03 14:14:47</t>
+          <t>2026-03-19 10:02:27</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-11-03 14:14:47</t>
+          <t>2026-03-19 10:02:27</t>
         </is>
       </c>
     </row>
@@ -536,123 +536,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-11-03 14:14:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1 Slot</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>600000</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2025-11-03 14:16:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>5 Slot</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2025-11-03 14:16:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>100 Slot</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>100</v>
-      </c>
-      <c r="E7" t="n">
-        <v>7</v>
-      </c>
-      <c r="F7" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2025-11-03 14:16:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>200 Slot</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>200</v>
-      </c>
-      <c r="E8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F8" t="n">
-        <v>95000000</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2025-11-03 14:16:43</t>
+          <t>2026-03-19 10:02:28</t>
         </is>
       </c>
     </row>

--- a/app/tests/plans_export.xlsx
+++ b/app/tests/plans_export.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-19 10:02:27</t>
+          <t>2026-03-19 16:25:11</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-19 10:02:27</t>
+          <t>2026-03-19 16:25:11</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-19 10:02:28</t>
+          <t>2026-03-19 16:25:11</t>
         </is>
       </c>
     </row>
